--- a/relationship_surveys/014_honor_in_family_dynamics--relationship_surveys.xlsx
+++ b/relationship_surveys/014_honor_in_family_dynamics--relationship_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>honor_in_family_dynamics</t>
+          <t>family_structure</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>what_is_honor</t>
+          <t>How do you describe your current family structure?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>family_structure</t>
+          <t>decision_making_process_husband</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>what_is_family</t>
+          <t>Do you always follow the advice of your husband/partner in decision-making?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>decision_making_process</t>
+          <t>honor_influence_family</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>how_do_decisions</t>
+          <t>How does the concept of honor influence your relationships within your family?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,23 +584,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>honor_influence</t>
+          <t>conflict_resolution_strategies</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>how_does_honor_influence</t>
+          <t>What are your conflict resolution strategies when disagreements arise within your family?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>conflict_resolution</t>
+          <t>relationship_expectations</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>how_do_youresolve</t>
+          <t>What do you expect from your relationships within your family?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,7 +630,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>how_do_you_feel</t>
+          <t>How do you feel when conflicts arise within your family?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>relationship_quality</t>
+          <t>conflict_resolution_effect</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>how_good</t>
+          <t>How do conflicts affect the dynamics of your family relationships?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>family_member_participation</t>
+          <t>honor_importance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>who_is_involved</t>
+          <t>How important is the concept of honor to you in your family relationships?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>honor_influence_level</t>
+          <t>honor_characteristics</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>level_of_honor</t>
+          <t>What are some key characteristics of honor in your family?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,40 +722,40 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>honor_influence_source</t>
+          <t>conflict_resolution_strategies_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>where_did_you_get</t>
+          <t>What conflict resolution strategies do you use in your family?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>honor_influence_type</t>
+          <t>conflict_resolution_effect_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>what_type_of_honor</t>
+          <t>How do you resolve conflicts within your family?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,23 +768,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>conflict_resolution_strategies</t>
+          <t>honor_factors</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>how_do_you_resolve</t>
+          <t>What factors influence the concept of honor in your family?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -796,35 +796,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>relationship_expectations</t>
+          <t>conflict_resolution_strategies_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>what_do_you_expect</t>
+          <t>Conflict Resolution Strategies 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>honor_influence_source</t>
+          <t>family_dynamics_description</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>where_did_you_get_honor</t>
+          <t>What are your family dynamics like?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>family_dynamics</t>
+          <t>honor_concept</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>what_are_family_dynamics</t>
+          <t>What is honor in your family?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>honor_value_scale</t>
+          <t>honor_value</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>how_important</t>
+          <t>What is the value of honor in your family?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>honor_importance</t>
+          <t>honor_definition</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>what_did_you_learn</t>
+          <t>What is the definition of honor in your family?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,182 +906,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>conflict_resolution_effect</t>
+          <t>honor_importance_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>how_do_conflicts_affect</t>
+          <t>Why is honor important in your family?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>honor_influence_factors</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>what_factors</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>family_dynamics_description</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>what_are_your_family_dynamics</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>honor_value</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>what_is_honor</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>honor_definition</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>what_is_honor</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>honor_concept</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>what_is_honor</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>honor_characteristics</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>what_characteristics</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>honor_importance_influence</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>why_is_honor</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,10 +937,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C63"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1131,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>mother</t>
+          <t>single_parent_family</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>mother</t>
+          <t>single parent family</t>
         </is>
       </c>
     </row>
@@ -1148,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>father</t>
+          <t>nuclear_family</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>father</t>
+          <t>nuclear family</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>sibling</t>
+          <t>extended_family</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>sibling</t>
+          <t>extended family</t>
         </is>
       </c>
     </row>
@@ -1182,998 +1021,709 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>other_relative</t>
+          <t>blended_family</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>other_relative</t>
+          <t>blended family</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>decision_making_process_choices</t>
+          <t>family_structure_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>always_follow_my_husband</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>always_follow_my_husband</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>decision_making_process_choices</t>
+          <t>honor_influence_family_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>always_follow_my_family</t>
+          <t>very_important</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>always_follow_my_family</t>
+          <t>very important</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>decision_making_process_choices</t>
+          <t>honor_influence_family_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>always_follow_my_parents</t>
+          <t>somewhat_important</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>always_follow_my_parents</t>
+          <t>somewhat important</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>decision_making_process_choices</t>
+          <t>honor_influence_family_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>always_follow_my_parents</t>
+          <t>not_very_important</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>always_follow_my_parents</t>
+          <t>not very important</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>decision_making_process_choices</t>
+          <t>honor_influence_family_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>always_follow_my_mother</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>always_follow_my_mother</t>
+          <t>not at all</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>decision_making_process_choices</t>
+          <t>conflict_resolution_strategies_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>always_follow_my_son</t>
+          <t>seek_help</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>always_follow_my_son</t>
+          <t>seek help</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>decision_making_process_choices</t>
+          <t>conflict_resolution_strategies_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>always_follow_my_wife</t>
+          <t>avoid</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>always_follow_my_wife</t>
+          <t>avoid</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>decision_making_process_choices</t>
+          <t>conflict_resolution_strategies_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>compromise</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>compromise</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>conflict_resolution_choices</t>
+          <t>conflict_resolution_strategies_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>always_argue</t>
+          <t>give_in</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>always_argue</t>
+          <t>give in</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>conflict_resolution_choices</t>
+          <t>conflict_resolution_strategies_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sometimes_argue</t>
+          <t>take</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>sometimes_argue</t>
+          <t>take</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>conflict_resolution_choices</t>
+          <t>relationship_expectations_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>rarely_argue</t>
+          <t>honesty</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>rarely_argue</t>
+          <t>honesty</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>conflict_resolution_choices</t>
+          <t>relationship_expectations_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>never_argue</t>
+          <t>respect</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>never_argue</t>
+          <t>respect</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>emotions_in_conflict_choices</t>
+          <t>relationship_expectations_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>angry</t>
+          <t>loyalty</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>angry</t>
+          <t>loyalty</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>emotions_in_conflict_choices</t>
+          <t>relationship_expectations_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sad</t>
+          <t>trust</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>sad</t>
+          <t>trust</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>emotions_in_conflict_choices</t>
+          <t>relationship_expectations_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>commitment</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>commitment</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>emotions_in_conflict_choices</t>
+          <t>relationship_expectations_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>relationship_quality_choices</t>
+          <t>emotions_in_conflict_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>angry</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>angry</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>relationship_quality_choices</t>
+          <t>emotions_in_conflict_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>bad</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>bad</t>
+          <t>sad</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>relationship_quality_choices</t>
+          <t>emotions_in_conflict_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>happy</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>family_member_participation_choices</t>
+          <t>emotions_in_conflict_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>family_member_participation_choices</t>
+          <t>conflict_resolution_effect_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>parents</t>
+          <t>affect_family_happiness</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>parents</t>
+          <t>affect family happiness</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>family_member_participation_choices</t>
+          <t>conflict_resolution_effect_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>children</t>
+          <t>affect_relationships_with_others</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>children</t>
+          <t>affect relationships with others</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>family_member_participation_choices</t>
+          <t>conflict_resolution_effect_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>spouse</t>
+          <t>have_no_effect</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>spouse</t>
+          <t>have no effect</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>family_member_participation_choices</t>
+          <t>honor_characteristics_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>trustworthyness</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>trustworthyness</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>honor_influence_source_choices</t>
+          <t>honor_characteristics_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>family</t>
+          <t>respect</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>family</t>
+          <t>respect</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>honor_influence_source_choices</t>
+          <t>honor_characteristics_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>friends</t>
+          <t>loyalty</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>friends</t>
+          <t>loyalty</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>honor_influence_source_choices</t>
+          <t>honor_characteristics_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>school</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>school</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>honor_influence_source_choices</t>
+          <t>conflict_resolution_strategies_2_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>seek_help</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>seek help</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>honor_influence_type_choices</t>
+          <t>conflict_resolution_strategies_2_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>cultural</t>
+          <t>avoid</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>cultural</t>
+          <t>avoid</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>honor_influence_type_choices</t>
+          <t>conflict_resolution_strategies_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>religious</t>
+          <t>compromise</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>religious</t>
+          <t>compromise</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>honor_influence_type_choices</t>
+          <t>conflict_resolution_strategies_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>societal</t>
+          <t>give_in</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>societal</t>
+          <t>give in</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>honor_influence_type_choices</t>
+          <t>conflict_resolution_strategies_2_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>personal</t>
+          <t>take</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>personal</t>
+          <t>take</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>conflict_resolution_strategies_choices</t>
+          <t>honor_factors_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>seek_help</t>
+          <t>cultural</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>seek_help</t>
+          <t>cultural</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>conflict_resolution_strategies_choices</t>
+          <t>honor_factors_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>avoid</t>
+          <t>religious</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>avoid</t>
+          <t>religious</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>conflict_resolution_strategies_choices</t>
+          <t>honor_factors_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>compromise</t>
+          <t>societal</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>compromise</t>
+          <t>societal</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>conflict_resolution_strategies_choices</t>
+          <t>honor_factors_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>give_in</t>
+          <t>personal</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>give_in</t>
+          <t>personal</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>conflict_resolution_strategies_choices</t>
+          <t>conflict_resolution_strategies_3_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>take</t>
+          <t>seek_help</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>take</t>
+          <t>seek help</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>relationship_expectations_choices</t>
+          <t>conflict_resolution_strategies_3_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>honesty</t>
+          <t>avoid</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>honesty</t>
+          <t>avoid</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>relationship_expectations_choices</t>
+          <t>conflict_resolution_strategies_3_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>respect</t>
+          <t>compromise</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>respect</t>
+          <t>compromise</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>relationship_expectations_choices</t>
+          <t>conflict_resolution_strategies_3_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>loyalty</t>
+          <t>give_in</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>loyalty</t>
+          <t>give in</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>relationship_expectations_choices</t>
+          <t>conflict_resolution_strategies_3_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>trust</t>
+          <t>take</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>trust</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>relationship_expectations_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>commitment</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>commitment</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>relationship_expectations_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>honor_influence_source_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>honor_influence_source_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>friends</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>friends</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>honor_influence_source_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>school</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>school</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>honor_influence_source_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>honor_value_scale_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>very_important</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>very_important</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>honor_value_scale_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>somewhat_important</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>somewhat_important</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>honor_value_scale_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>not_very_important</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>not_very_important</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>honor_value_scale_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>not_at_all</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>not_at_all</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>conflict_resolution_effect_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>affect_family_happiness</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>affect_family_happiness</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>conflict_resolution_effect_choices</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>affect_relationships_with_others</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>affect_relationships_with_others</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>conflict_resolution_effect_choices</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>have_no_effect</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>have_no_effect</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>honor_characteristics_choices</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>trustworthyness</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>trustworthyness</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>honor_characteristics_choices</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>respect</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>respect</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>honor_characteristics_choices</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>loyalty</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>loyalty</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>honor_characteristics_choices</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>other</t>
+          <t>take</t>
         </is>
       </c>
     </row>
